--- a/data/trans_camb/P1426-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1426-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,87</t>
+          <t>0,09; 2,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,97</t>
+          <t>2,5; 5,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,19</t>
+          <t>-1,43; 2,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,64</t>
+          <t>0,12; 3,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,15</t>
+          <t>-0,22; 1,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,25</t>
+          <t>1,98; 4,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1662,56%</t>
+          <t>1628,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146,57%</t>
+          <t>158,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>450,07%</t>
+          <t>454,42%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 424,02</t>
+          <t>-79,27; 565,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 851,78</t>
+          <t>-12,41; 892,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 732,28</t>
+          <t>-39,71; 645,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>123,08; 1467,66</t>
+          <t>137,95; 1552,54</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,61</t>
+          <t>-2,14; 0,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,63</t>
+          <t>1,39; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,57</t>
+          <t>-2,65; 1,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,27</t>
+          <t>-1,39; 2,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,66</t>
+          <t>-1,72; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,63</t>
+          <t>0,76; 3,47</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>304,69%</t>
+          <t>293,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>158,03%</t>
+          <t>150,29%</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,34; 1497,3</t>
+          <t>33,89; 1683,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 280,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 354,97</t>
+          <t>-55,01; 362,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,75; 100,86</t>
+          <t>-84,27; 153,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 480,2</t>
+          <t>23,21; 438,48</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,61</t>
+          <t>-1,77; 1,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,01</t>
+          <t>0,49; 5,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,96</t>
+          <t>-1,52; 4,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,47</t>
+          <t>-0,16; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,59</t>
+          <t>-1,4; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,59</t>
+          <t>0,88; 4,19</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>133,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156,14%</t>
+          <t>144,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>136,41%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 137,14</t>
+          <t>-64,6; 140,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 271,17</t>
+          <t>10,63; 438,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 914,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 971,96</t>
+          <t>-37,97; 866,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,09; 123,51</t>
+          <t>-52,11; 124,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 241,89</t>
+          <t>28,06; 325,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>3,33</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,07</t>
+          <t>-1,06; 1,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,82</t>
+          <t>2,81; 5,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,39</t>
+          <t>-0,77; 1,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,79</t>
+          <t>0,88; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,86</t>
+          <t>-0,66; 0,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,99</t>
+          <t>2,36; 4,35</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>254,44%</t>
+          <t>252,97%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155,22%</t>
+          <t>213,6%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>205,2%</t>
+          <t>235,09%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 94,17</t>
+          <t>-49,14; 98,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>122,54; 504,4</t>
+          <t>110,52; 482,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 294,01</t>
+          <t>-54,25; 317,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 491,62</t>
+          <t>36,28; 686,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 80,0</t>
+          <t>-37,92; 94,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,87; 391,06</t>
+          <t>120,59; 449,11</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>3,85</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,28</t>
+          <t>-2,24; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,18</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,6</t>
+          <t>-1,06; 1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,08</t>
+          <t>3,64; 6,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,17</t>
+          <t>-1,11; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,22</t>
+          <t>2,66; 5,06</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>112,01%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306,7%</t>
+          <t>345,01%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>206,71%</t>
+          <t>205,75%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,72; 99,8</t>
+          <t>-64,54; 86,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,46; 334,06</t>
+          <t>-6,93; 269,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 164,97</t>
+          <t>-53,77; 177,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89,2; 726,47</t>
+          <t>140,34; 831,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 92,92</t>
+          <t>-45,61; 84,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,87; 408,92</t>
+          <t>94,45; 412,64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,67</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,0</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,1</t>
+          <t>-2,66; 1,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,75</t>
+          <t>-1,36; 1,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,66</t>
+          <t>1,64; 5,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,19</t>
+          <t>-1,31; 1,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,22</t>
+          <t>1,22; 3,95</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123,41%</t>
+          <t>118,06%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>105,88%</t>
+          <t>106,24%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 76,78</t>
+          <t>-39,12; 74,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47,26; 260,85</t>
+          <t>39,04; 235,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 65,95</t>
+          <t>-40,44; 60,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,05; 224,87</t>
+          <t>37,7; 204,81</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,16</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,55</t>
+          <t>-0,71; 0,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,82</t>
+          <t>2,45; 3,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,83</t>
+          <t>-0,53; 0,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>2,08; 3,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,49</t>
+          <t>-0,46; 0,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,43</t>
+          <t>2,48; 3,55</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>193,44%</t>
+          <t>205,04%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135,61%</t>
+          <t>152,21%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>161,29%</t>
+          <t>175,71%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 43,7</t>
+          <t>-37,7; 36,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>100,37; 305,24</t>
+          <t>128,87; 334,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 53,59</t>
+          <t>-24,84; 60,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>73,5; 216,01</t>
+          <t>90,98; 229,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 32,45</t>
+          <t>-23,35; 35,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>107,44; 232,99</t>
+          <t>125,28; 244,43</t>
         </is>
       </c>
     </row>
